--- a/AFTER onedrive is back/cutoverValidation.xlsx
+++ b/AFTER onedrive is back/cutoverValidation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infogain-my.sharepoint.com/personal/rodrigo_jasinski_infogain_com/Documents/TASKS/AFTER onedrive is back/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mihub-my.sharepoint.com/personal/rodrigo_jasinski_mitchell_com/Documents/Documents/GitHub/tenarai/AFTER onedrive is back/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{7175D29E-3FCA-4CCA-82E0-3548724ED44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62050075-7414-40FC-8808-B6A06814B78E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{7FC7A751-34BA-482F-9996-E427E5FE8A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F5810A-E5B9-4156-8D92-708D59963A11}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-4845" windowWidth="38640" windowHeight="16440" xr2:uid="{E68994BB-B547-46C3-9D76-D8D9CAF12D71}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="103">
   <si>
     <t>script name</t>
   </si>
@@ -82,18 +82,12 @@
     <t>no change</t>
   </si>
   <si>
-    <t>do I have the correct version?</t>
-  </si>
-  <si>
     <t>mptr300.ksh</t>
   </si>
   <si>
     <t>change echo to print</t>
   </si>
   <si>
-    <t>do we need this change?</t>
-  </si>
-  <si>
     <t>oem_job_datafile_prep.ksh</t>
   </si>
   <si>
@@ -127,15 +121,9 @@
     <t>is this OK to hard code service account?</t>
   </si>
   <si>
-    <t>export PATH=/home/production.int/svc-apd-race-prd:/prod/race/oem/bin:/prod/race/share/bin:$PATH</t>
-  </si>
-  <si>
     <t>raceftp.ksh</t>
   </si>
   <si>
-    <t>set FTP_SFTP_USER user id for prod</t>
-  </si>
-  <si>
     <t>rcheck_out</t>
   </si>
   <si>
@@ -310,45 +298,21 @@
     <t>mptz999</t>
   </si>
   <si>
-    <t>LOG variable setup in race_ext, removed log creation</t>
-  </si>
-  <si>
-    <t>removed log creation, left as is</t>
-  </si>
-  <si>
-    <t>Need to retest</t>
-  </si>
-  <si>
     <t>race_ext.ksh</t>
   </si>
   <si>
-    <t>Added $LOG variable declaration</t>
-  </si>
-  <si>
-    <t>No need to change, deleted from deliverables</t>
-  </si>
-  <si>
-    <t>to test</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
     <t>oem_research replacement</t>
   </si>
   <si>
-    <t>NEED TO REMOVE FROM CODE BEFORE TEST: EXPORT path</t>
-  </si>
-  <si>
     <t>no CHANGES NEEDED, REMOVED FROM DELIVERABLES</t>
   </si>
   <si>
     <t>prod move done</t>
   </si>
   <si>
-    <t>to remove from the log ?</t>
-  </si>
-  <si>
     <t>xex999.ksh</t>
   </si>
   <si>
@@ -370,29 +334,27 @@
     <t>change continue to next</t>
   </si>
   <si>
-    <t>from where FTP_SFTP_USER comes ?</t>
-  </si>
-  <si>
-    <r>
-      <t>check_out.ksh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (stopped here)</t>
-    </r>
+    <t>check_out.ksh</t>
+  </si>
+  <si>
+    <t>[ -s "$LOG" ] &amp;&amp; cat "$LOG"          # rj132422 - show sqlplus output in the job log
+[ -n "$LOG_TMP" ] &amp;&amp; rm -f "$LOG"    # rj132422 - only remove the log this script created</t>
+  </si>
+  <si>
+    <t>rpt_log_retention.ksh - CHECK THE LOG AFTER THE radp AWS TEST</t>
+  </si>
+  <si>
+    <t>Rodrigo Jasinski - can you add these 3 .prm files to your list of changes and make the change (checkout, change, checkin)?</t>
+  </si>
+  <si>
+    <t>1 Like reaction.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,13 +385,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -448,8 +403,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,8 +442,13 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -480,28 +456,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
@@ -513,18 +502,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Check Cell" xfId="4" builtinId="23"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,9 +551,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>450937</xdr:colOff>
+      <xdr:colOff>450938</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>215801</xdr:rowOff>
+      <xdr:rowOff>318377</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -598,8 +596,8 @@
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>107477</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>292223</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>673224</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -628,6 +626,128 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="👍">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724C40B9-4AD1-7324-2BAA-7801519A5275}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="17964150"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>256761</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>8624465</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>186040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1AC4C1-4E93-C98E-BA86-E14FA2CE694B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="256761" y="17087022"/>
+          <a:ext cx="8367704" cy="2596279"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -952,87 +1072,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6D3116-D246-4CA9-9A7B-34465EAFBEF4}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="132.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3"/>
-    <col min="3" max="3" width="56.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="132.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2"/>
+    <col min="3" max="3" width="56.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="10" max="10" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1043,28 +1152,22 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1073,59 +1176,51 @@
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>16</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>68</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
@@ -1133,283 +1228,294 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="99" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="6" t="s">
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" ht="33.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="99" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="99" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="6" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="10"/>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
       <c r="D26" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
       <c r="D29" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
       <c r="D30" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" ht="66" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="B34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" ht="33" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" ht="66" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="1" t="s">
-        <v>54</v>
-      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C42"/>
     </row>
     <row r="61" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
+      <c r="A61" s="3"/>
     </row>
     <row r="62" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
+      <c r="A62" s="3"/>
     </row>
     <row r="63" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
+      <c r="A63" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
@@ -1419,12 +1525,6 @@
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="B24:B30"/>
     <mergeCell ref="C24:C30"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1446,7 +1546,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1454,19 +1554,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1476,325 +1576,325 @@
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="6" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="C12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="E12" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>101</v>
+      <c r="D14" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>101</v>
+      <c r="A16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>101</v>
+      <c r="B25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D27" s="1"/>
     </row>
@@ -1811,25 +1911,272 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BDCB214F5EDC594985EC8ABE303D0D17" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c71fb8b00bbfcab7bfe4b0436ef7f65b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="47f21630-82e3-4b9a-80ed-e5164a9b6bff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecabba4666265743e4476985e218bbd4" ns3:_="">
+    <xsd:import namespace="47f21630-82e3-4b9a-80ed-e5164a9b6bff"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="47f21630-82e3-4b9a-80ed-e5164a9b6bff" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="9" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="47f21630-82e3-4b9a-80ed-e5164a9b6bff" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8870841E-F902-4D57-8198-AB52924CAE80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="47f21630-82e3-4b9a-80ed-e5164a9b6bff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BFAD340-2F3F-4B58-B0F0-9779D9FB1002}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{824A80F8-6CE9-4393-8CBD-8A2679DC77FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="47f21630-82e3-4b9a-80ed-e5164a9b6bff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a05ad2a3-a46b-4292-b07b-b6cecb98b8f6}" enabled="0" method="" siteId="{a05ad2a3-a46b-4292-b07b-b6cecb98b8f6}" removed="1"/>
+</clbl:labelList>
 </file>